--- a/output/full_scan/batch_seq1_2026-08-11.xlsx
+++ b/output/full_scan/batch_seq1_2026-08-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O132"/>
+  <dimension ref="A1:O133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1852,21 +1852,21 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1526</v>
+        <v>1515</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>428.4759109220414</v>
+        <v>439.8770648506869</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>19</v>
+        <v>31.2</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>62.75214711496405</v>
+        <v>46.72458537026104</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>47.07115644144011</v>
+        <v>28.31322714400099</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.6138151680119505</v>
+        <v>0.8149748214244018</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.0552545326348695</v>
+        <v>-0.4343200920012054</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1309</v>
+        <v>1526</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>411.1471602673082</v>
+        <v>428.4759109220414</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>41.52723007550689</v>
+        <v>62.75214711496405</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>17.19347174560159</v>
+        <v>47.07115644144011</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.2595805477207436</v>
+        <v>0.6138151680119505</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.0060577706939364</v>
+        <v>0.0552545326348695</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1432</v>
+        <v>1309</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>405.078930911528</v>
+        <v>411.1471602673082</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>15.3</v>
+        <v>13</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>50.95505930945949</v>
+        <v>41.52723007550689</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>25.75021420284398</v>
+        <v>17.19347174560159</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.7003565239209463</v>
+        <v>0.2595805477207436</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.081368304773151</v>
+        <v>0.0060577706939364</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1513</v>
+        <v>1432</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>400.5229534332893</v>
+        <v>405.078930911528</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>160.5</v>
+        <v>15.3</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>49.04047904672418</v>
+        <v>50.95505930945949</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>22.50604274131634</v>
+        <v>25.75021420284398</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5462464149368093</v>
+        <v>0.7003565239209463</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.9065710135636152</v>
+        <v>0.081368304773151</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1229</v>
+        <v>1513</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>398.7253107875764</v>
+        <v>400.5229534332893</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>41.9</v>
+        <v>160.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>57.24037125149674</v>
+        <v>49.04047904672418</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>11.16007037440771</v>
+        <v>22.50604274131634</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.245792503546678</v>
+        <v>0.5462464149368093</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.1007382603771434</v>
+        <v>0.9065710135636152</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1216</v>
+        <v>1229</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>398.297000859084</v>
+        <v>398.7253107875764</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>75.90000000000001</v>
+        <v>41.9</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>50.1964409922735</v>
+        <v>57.24037125149674</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>20.99773696870421</v>
+        <v>11.16007037440771</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.5454149520786722</v>
+        <v>1.245792503546678</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.1884441727940486</v>
+        <v>0.1007382603771434</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1203</v>
+        <v>1216</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>393.2520897619105</v>
+        <v>398.297000859084</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>45.95</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>46.64434885790448</v>
+        <v>50.1964409922735</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>17.41118151636101</v>
+        <v>20.99773696870421</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.349592415381889</v>
+        <v>0.5454149520786722</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.3570210599754435</v>
+        <v>-0.1884441727940486</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1402</v>
+        <v>1203</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>386.539634412052</v>
+        <v>393.2520897619105</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>27.3</v>
+        <v>45.95</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>49.20603350020566</v>
+        <v>46.64434885790448</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>14.80699676704839</v>
+        <v>17.41118151636101</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.037191326958304</v>
+        <v>0.349592415381889</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0206040355552508</v>
+        <v>-0.3570210599754435</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1301</v>
+        <v>1402</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>378.0401564785786</v>
+        <v>386.539634412052</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>55.6</v>
+        <v>27.3</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>46.74057288099788</v>
+        <v>49.20603350020566</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>15.20039199896169</v>
+        <v>14.80699676704839</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.3120562285440211</v>
+        <v>1.037191326958304</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.7035811163955719</v>
+        <v>0.0206040355552508</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1236</v>
+        <v>1301</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>375.1119844147829</v>
+        <v>378.0401564785786</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>25.2</v>
+        <v>55.6</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>59.5586556866246</v>
+        <v>46.74057288099788</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>19.06234052027171</v>
+        <v>15.20039199896169</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.280616226502821</v>
+        <v>0.3120562285440211</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.2274209289217866</v>
+        <v>-0.7035811163955719</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1442</v>
+        <v>1236</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>374.655718306141</v>
+        <v>375.1119844147829</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>29.85</v>
+        <v>25.2</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>57.23588554203469</v>
+        <v>59.5586556866246</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>24.24708991662144</v>
+        <v>19.06234052027171</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.2412429812893633</v>
+        <v>1.280616226502821</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.0395705337941666</v>
+        <v>0.2274209289217866</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1439</v>
+        <v>1442</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>373.8135866675879</v>
+        <v>374.655718306141</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>28.85</v>
+        <v>29.85</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>61.84972237186542</v>
+        <v>57.23588554203469</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>16.31728842823736</v>
+        <v>24.24708991662144</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3918968276735593</v>
+        <v>0.2412429812893633</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.1443541984183658</v>
+        <v>-0.0395705337941666</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1220</v>
+        <v>1439</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>373.776142573578</v>
+        <v>373.8135866675879</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>11.15</v>
+        <v>28.85</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>33.45802888711818</v>
+        <v>61.84972237186542</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>34.97124943750534</v>
+        <v>16.31728842823736</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.2328142041653543</v>
+        <v>0.3918968276735593</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0021448243131632</v>
+        <v>0.1443541984183658</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1524</v>
+        <v>1220</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>370.7749466919198</v>
+        <v>373.776142573578</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>27.2</v>
+        <v>11.15</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>50.22102785127304</v>
+        <v>33.45802888711818</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>28.81970801030623</v>
+        <v>34.97124943750534</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.535257575535256</v>
+        <v>0.2328142041653543</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.2434948686576256</v>
+        <v>0.0021448243131632</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1210</v>
+        <v>1524</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>369.1782588013367</v>
+        <v>370.7749466919198</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>53.9</v>
+        <v>27.2</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>38.17190071174548</v>
+        <v>50.22102785127304</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>30.88333434699631</v>
+        <v>28.81970801030623</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.034942097131946</v>
+        <v>0.535257575535256</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.5138513427947438</v>
+        <v>0.2434948686576256</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1472</v>
+        <v>1210</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>367.9269438148242</v>
+        <v>369.1782588013367</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>89</v>
+        <v>53.9</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>51.75909569405253</v>
+        <v>38.17190071174548</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>9.650250644180369</v>
+        <v>30.88333434699631</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.2428603462103321</v>
+        <v>1.034942097131946</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1.335599387906937</v>
+        <v>-0.5138513427947438</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1514</v>
+        <v>1472</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>365.3196194390216</v>
+        <v>367.9269438148242</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>43.1768601429351</v>
+        <v>51.75909569405253</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>26.10629698568654</v>
+        <v>9.650250644180369</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.4937826619144091</v>
+        <v>0.2428603462103321</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.7221265755818056</v>
+        <v>1.335599387906937</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1342</v>
+        <v>1514</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>361.527173571217</v>
+        <v>365.3196194390216</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>102.5</v>
+        <v>102</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>42.56748006451972</v>
+        <v>43.1768601429351</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>28.56495767453353</v>
+        <v>26.10629698568654</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.4496404737020364</v>
+        <v>0.4937826619144091</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.3807760402849149</v>
+        <v>0.7221265755818056</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1437</v>
+        <v>1342</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>360.5152994955215</v>
+        <v>361.527173571217</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>30.4</v>
+        <v>102.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>48.54091658269144</v>
+        <v>42.56748006451972</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>19.33954860545237</v>
+        <v>28.56495767453353</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.4609809680333634</v>
+        <v>0.4496404737020364</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.1566334052246537</v>
+        <v>-0.3807760402849149</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1568</v>
+        <v>1437</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>349.958833619381</v>
+        <v>360.5152994955215</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>28.5</v>
+        <v>30.4</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>41.45675142900744</v>
+        <v>48.54091658269144</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>22.74065462889284</v>
+        <v>19.33954860545237</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.4044884569132074</v>
+        <v>0.4609809680333634</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.4319178457368897</v>
+        <v>-0.1566334052246537</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1326</v>
+        <v>1568</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>346.9668781509539</v>
+        <v>349.958833619381</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>58.2</v>
+        <v>28.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>45.62903804524353</v>
+        <v>41.45675142900744</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15.27378242141762</v>
+        <v>22.74065462889284</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.3405708815890401</v>
+        <v>0.4044884569132074</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.8319722537334188</v>
+        <v>0.4319178457368897</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1477</v>
+        <v>1326</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>335.9926556225922</v>
+        <v>346.9668781509539</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>221.5</v>
+        <v>58.2</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>51.31739932203453</v>
+        <v>45.62903804524353</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>11.5375287315453</v>
+        <v>15.27378242141762</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.9441080317692208</v>
+        <v>0.3405708815890401</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.6385130704933423</v>
+        <v>-0.8319722537334188</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1455</v>
+        <v>1477</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>334.4210033697305</v>
+        <v>335.9926556225922</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>9.6</v>
+        <v>221.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>57.64588278442741</v>
+        <v>51.31739932203453</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>18.68329344736921</v>
+        <v>11.5375287315453</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.910325167968465</v>
+        <v>0.9441080317692208</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.1046472799546037</v>
+        <v>0.6385130704933423</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1582</v>
+        <v>1455</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>333.5994793960298</v>
+        <v>334.4210033697305</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>75.3</v>
+        <v>9.6</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>52.16051432114149</v>
+        <v>57.64588278442741</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>33.28133515949956</v>
+        <v>18.68329344736921</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.9692951731219532</v>
+        <v>1.910325167968465</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1.645062561429473</v>
+        <v>0.1046472799546037</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1321</v>
+        <v>1582</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>332.9561939333805</v>
+        <v>333.5994793960298</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>31.95</v>
+        <v>75.3</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>52.38864746754686</v>
+        <v>52.16051432114149</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>14.93644998228591</v>
+        <v>33.28133515949956</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.6188012648599847</v>
+        <v>0.9692951731219532</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.0609971870093484</v>
+        <v>1.645062561429473</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1560</v>
+        <v>1321</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>328.4934397084596</v>
+        <v>332.9561939333805</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>687</v>
+        <v>31.95</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>51.63913589547047</v>
+        <v>52.38864746754686</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>13.29765053865357</v>
+        <v>14.93644998228591</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4777662974194765</v>
+        <v>0.6188012648599847</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>4.338954788992442</v>
+        <v>-0.0609971870093484</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1435</v>
+        <v>1560</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>325.7701195109184</v>
+        <v>328.4934397084596</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>23.6</v>
+        <v>687</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>51.82647333983666</v>
+        <v>51.63913589547047</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>8.066518233274861</v>
+        <v>13.29765053865357</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.236170837135644</v>
+        <v>0.4777662974194765</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.0872474229168677</v>
+        <v>4.338954788992442</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1325</v>
+        <v>1435</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>324.263616200573</v>
+        <v>325.7701195109184</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>26.3</v>
+        <v>23.6</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>50.54850454000123</v>
+        <v>51.82647333983666</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>24.90075748257971</v>
+        <v>8.066518233274861</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.3872299629085262</v>
+        <v>1.236170837135644</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0012671451922932</v>
+        <v>-0.0872474229168677</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1416</v>
+        <v>1325</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>320.3588606533316</v>
+        <v>324.263616200573</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>10.95</v>
+        <v>26.3</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>50.46517771063932</v>
+        <v>50.54850454000123</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>22.57730660233251</v>
+        <v>24.90075748257971</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.6756232447876569</v>
+        <v>0.3872299629085262</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0204150409481747</v>
+        <v>0.0012671451922932</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1413</v>
+        <v>1416</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>319.9092469134781</v>
+        <v>320.3588606533316</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>9.49</v>
+        <v>10.95</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>49.82702655094291</v>
+        <v>50.46517771063932</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>16.69493946805939</v>
+        <v>22.57730660233251</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.0387677475666024</v>
+        <v>0.6756232447876569</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.0351350246016526</v>
+        <v>0.0204150409481747</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1522</v>
+        <v>1413</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>314.659843995527</v>
+        <v>319.9092469134781</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>28.25</v>
+        <v>9.49</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>45.60192400140237</v>
+        <v>49.82702655094291</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>22.07775329046874</v>
+        <v>16.69493946805939</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.779767028247413</v>
+        <v>0.0387677475666024</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.12716147982228</v>
+        <v>-0.0351350246016526</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1436</v>
+        <v>1522</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>313.8827628490332</v>
+        <v>314.659843995527</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>37.25</v>
+        <v>28.25</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>36.26396605298567</v>
+        <v>45.60192400140237</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>37.38851424097656</v>
+        <v>22.07775329046874</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.228140315722467</v>
+        <v>0.779767028247413</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.1030838199030017</v>
+        <v>0.12716147982228</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1468</v>
+        <v>1436</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>310.9208066965225</v>
+        <v>313.8827628490332</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>13.4</v>
+        <v>37.25</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.20630094666465</v>
+        <v>36.26396605298567</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>31.52311768412051</v>
+        <v>37.38851424097656</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.5578539685977438</v>
+        <v>0.228140315722467</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.068014350225212</v>
+        <v>0.1030838199030017</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1533</v>
+        <v>1468</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>310.1160157782964</v>
+        <v>310.9208066965225</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>32.1</v>
+        <v>13.4</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>39.55794984681347</v>
+        <v>52.20630094666465</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>30.25908270005224</v>
+        <v>31.52311768412051</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.301004634303973</v>
+        <v>0.5578539685977438</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.1399299995070516</v>
+        <v>-0.068014350225212</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1519</v>
+        <v>1533</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>307.637314419185</v>
+        <v>310.1160157782964</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>703</v>
+        <v>32.1</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>49.36152926987168</v>
+        <v>39.55794984681347</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>27.42060686359899</v>
+        <v>30.25908270005224</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.388798476689908</v>
+        <v>1.301004634303973</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>4.003224569744347</v>
+        <v>0.1399299995070516</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1215</v>
+        <v>1519</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>305.6854120135607</v>
+        <v>307.637314419185</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>109</v>
+        <v>703</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>48.76907478001936</v>
+        <v>49.36152926987168</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>43.24224320662321</v>
+        <v>27.42060686359899</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.8570895229183785</v>
+        <v>1.388798476689908</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.7469003322494432</v>
+        <v>4.003224569744347</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1467</v>
+        <v>1215</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>305.0546136737315</v>
+        <v>305.6854120135607</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>9.17</v>
+        <v>109</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>48.53640688787144</v>
+        <v>48.76907478001936</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>17.32432939492621</v>
+        <v>43.24224320662321</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.6055603243375735</v>
+        <v>0.8570895229183785</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.1112893337336087</v>
+        <v>0.7469003322494432</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1418</v>
+        <v>1467</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>300.0311915161025</v>
+        <v>305.0546136737315</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>18</v>
+        <v>9.17</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>44.72896997235359</v>
+        <v>48.53640688787144</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>20.00581859068063</v>
+        <v>17.32432939492621</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.1250649643009007</v>
+        <v>0.6055603243375735</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.0467437114203713</v>
+        <v>-0.1112893337336087</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1506</v>
+        <v>1418</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>295.6373793354758</v>
+        <v>300.0311915161025</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>10.6</v>
+        <v>18</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>53.65486434981683</v>
+        <v>44.72896997235359</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>22.568653942497</v>
+        <v>20.00581859068063</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.662196137200293</v>
+        <v>0.1250649643009007</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.0147692095457922</v>
+        <v>-0.0467437114203713</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1503</v>
+        <v>1506</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>293.4261847870686</v>
+        <v>295.6373793354758</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>197</v>
+        <v>10.6</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>43.6172329224509</v>
+        <v>53.65486434981683</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>27.79524027812574</v>
+        <v>22.568653942497</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.9296184789241294</v>
+        <v>0.662196137200293</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.812910899986603</v>
+        <v>-0.0147692095457922</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1463</v>
+        <v>1503</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>291.2907683733289</v>
+        <v>293.4261847870686</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>17.85</v>
+        <v>197</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>52.73546460473577</v>
+        <v>43.6172329224509</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>14.36679042525562</v>
+        <v>27.79524027812574</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5434658532705821</v>
+        <v>0.9296184789241294</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.0034416952710157</v>
+        <v>0.812910899986603</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1476</v>
+        <v>1463</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>280.4916981673899</v>
+        <v>291.2907683733289</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>332</v>
+        <v>17.85</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>44.65722516107578</v>
+        <v>52.73546460473577</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>19.3404422990824</v>
+        <v>14.36679042525562</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.8896667997248175</v>
+        <v>0.5434658532705821</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-1.00678659863362</v>
+        <v>-0.0034416952710157</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1536</v>
+        <v>1476</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>275.6339257801737</v>
+        <v>280.4916981673899</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>51.2</v>
+        <v>332</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>53.22227897639052</v>
+        <v>44.65722516107578</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>13.69494818252926</v>
+        <v>19.3404422990824</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.5003160922249125</v>
+        <v>0.8896667997248175</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.3159899699966763</v>
+        <v>-1.00678659863362</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1102</v>
+        <v>1536</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>272.4557755880668</v>
+        <v>275.6339257801737</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>32.45</v>
+        <v>51.2</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>38.52383346215739</v>
+        <v>53.22227897639052</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>28.43353066573429</v>
+        <v>13.69494818252926</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5836679658648454</v>
+        <v>0.5003160922249125</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0405050734409524</v>
+        <v>0.3159899699966763</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>271.9993124605894</v>
+        <v>272.4557755880668</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>11.85</v>
+        <v>32.45</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>29.19594336004857</v>
+        <v>38.52383346215739</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>56.14770979138584</v>
+        <v>28.43353066573429</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.976228750469454</v>
+        <v>0.5836679658648454</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0409320313520392</v>
+        <v>0.0405050734409524</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1409</v>
+        <v>1108</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>270.9907741070269</v>
+        <v>271.9993124605894</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>24.25</v>
+        <v>11.85</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>52.66905792945346</v>
+        <v>29.19594336004857</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>18.25778491805627</v>
+        <v>56.14770979138584</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>2.177057795327413</v>
+        <v>1.976228750469454</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.2752931197043329</v>
+        <v>0.0409320313520392</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1304</v>
+        <v>1409</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>270.5004804779987</v>
+        <v>270.9907741070269</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>11.95</v>
+        <v>24.25</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>44.62243479569965</v>
+        <v>52.66905792945346</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15.99394048986938</v>
+        <v>18.25778491805627</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.4092229600487194</v>
+        <v>2.177057795327413</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0265786774749629</v>
+        <v>0.2752931197043329</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1475</v>
+        <v>1304</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>266.432064011262</v>
+        <v>270.5004804779987</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>27.15</v>
+        <v>11.95</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>51.16923656774865</v>
+        <v>44.62243479569965</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>10.78818503948649</v>
+        <v>15.99394048986938</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.808096588343658</v>
+        <v>0.4092229600487194</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.00694925957315</v>
+        <v>0.0265786774749629</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1438</v>
+        <v>1475</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>264.0955427232427</v>
+        <v>266.432064011262</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>22.45</v>
+        <v>27.15</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>52.23340084143064</v>
+        <v>51.16923656774865</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>16.29996512183295</v>
+        <v>10.78818503948649</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.3929952472616391</v>
+        <v>1.808096588343658</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.009462815416149699</v>
+        <v>0.00694925957315</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1233</v>
+        <v>1438</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>259.9502512096455</v>
+        <v>264.0955427232427</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>28</v>
+        <v>22.45</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>36.81477639092548</v>
+        <v>52.23340084143064</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>32.07628624210136</v>
+        <v>16.29996512183295</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.014648476212135</v>
+        <v>0.3929952472616391</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.1111812470943652</v>
+        <v>0.009462815416149699</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1313</v>
+        <v>1233</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>259.4469976615495</v>
+        <v>259.9502512096455</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>11.3</v>
+        <v>28</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>47.18557367471468</v>
+        <v>36.81477639092548</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>18.98486064721317</v>
+        <v>32.07628624210136</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.5511560768368882</v>
+        <v>1.014648476212135</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0364108069190954</v>
+        <v>-0.1111812470943652</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1227</v>
+        <v>1313</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>253.8586762490984</v>
+        <v>259.4469976615495</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>28.9</v>
+        <v>11.3</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>44.17793449682099</v>
+        <v>47.18557367471468</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>16.52284409359486</v>
+        <v>18.98486064721317</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5803277779561153</v>
+        <v>0.5511560768368882</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.0743668604423379</v>
+        <v>0.0364108069190954</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1338</v>
+        <v>1227</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>252.9277541118056</v>
+        <v>253.8586762490984</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>15.15</v>
+        <v>28.9</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>36.13085969525946</v>
+        <v>44.17793449682099</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>36.5596882507276</v>
+        <v>16.52284409359486</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>3.049368076886422</v>
+        <v>0.5803277779561153</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0135561217104166</v>
+        <v>-0.0743668604423379</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1528</v>
+        <v>1338</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>246.4752653612645</v>
+        <v>252.9277541118056</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>19</v>
+        <v>15.15</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>42.04039258691191</v>
+        <v>36.13085969525946</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>41.87905566255956</v>
+        <v>36.5596882507276</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.6875115567800089</v>
+        <v>3.049368076886422</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.3047031127828075</v>
+        <v>-0.0135561217104166</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1504</v>
+        <v>1528</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>245.4422143653678</v>
+        <v>246.4752653612645</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>19</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>51.45156067236398</v>
+        <v>42.04039258691191</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>11.57477797473525</v>
+        <v>41.87905566255956</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.444833505570157</v>
+        <v>0.6875115567800089</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.4623565815650583</v>
+        <v>0.3047031127828075</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1446</v>
+        <v>1504</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>243.1136378083713</v>
+        <v>245.4422143653678</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>14</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>38.42219195091725</v>
+        <v>51.45156067236398</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>39.28842303972318</v>
+        <v>11.57477797473525</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.4005502340837044</v>
+        <v>0.444833505570157</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.1058207990009343</v>
+        <v>0.4623565815650583</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1529</v>
+        <v>1446</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>242.1320414974783</v>
+        <v>243.1136378083713</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>16.9</v>
+        <v>14</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>28.46181352921619</v>
+        <v>38.42219195091725</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>36.92616172379231</v>
+        <v>39.28842303972318</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.6761317741182674</v>
+        <v>0.4005502340837044</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.0435452993768699</v>
+        <v>0.1058207990009343</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1456</v>
+        <v>1529</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>231.2259258617373</v>
+        <v>242.1320414974783</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>13.8</v>
+        <v>16.9</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>46.16011168106276</v>
+        <v>28.46181352921619</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>13.32326001596232</v>
+        <v>36.92616172379231</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.9248609937212076</v>
+        <v>0.6761317741182674</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0223855591722976</v>
+        <v>0.0435452993768699</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1104</v>
+        <v>1456</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>230.1318115532384</v>
+        <v>231.2259258617373</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>26.65</v>
+        <v>13.8</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>44.87824851463436</v>
+        <v>46.16011168106276</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>15.47584064855316</v>
+        <v>13.32326001596232</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.5877999785201938</v>
+        <v>0.9248609937212076</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0351395249502984</v>
+        <v>0.0223855591722976</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1532</v>
+        <v>1104</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>229.7050742228243</v>
+        <v>230.1318115532384</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>21.85</v>
+        <v>26.65</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>42.03586421936555</v>
+        <v>44.87824851463436</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>27.00587128638867</v>
+        <v>15.47584064855316</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.4794046410191419</v>
+        <v>0.5877999785201938</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.089367138876109</v>
+        <v>0.0351395249502984</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1535</v>
+        <v>1532</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>中宇</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>227.9082928094179</v>
+        <v>229.7050742228243</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>46.05</v>
+        <v>21.85</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>39.44157396367929</v>
+        <v>42.03586421936555</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>19.1260934601327</v>
+        <v>27.00587128638867</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.5501484551371674</v>
+        <v>0.4794046410191419</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0954324712378362</v>
+        <v>-0.089367138876109</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1225</v>
+        <v>1535</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>219.3071323708781</v>
+        <v>227.9082928094179</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>24.6</v>
+        <v>46.05</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>36.55030615302968</v>
+        <v>39.44157396367929</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>33.10128009326493</v>
+        <v>19.1260934601327</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.7221247272283944</v>
+        <v>0.5501484551371674</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0455162045524704</v>
+        <v>0.0954324712378362</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>219.2130601496071</v>
+        <v>219.3071323708781</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>10.85</v>
+        <v>24.6</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>29.84984847644951</v>
+        <v>36.55030615302968</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>32.41562580832303</v>
+        <v>33.10128009326493</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.4333886196584854</v>
+        <v>0.7221247272283944</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0493446006715273</v>
+        <v>-0.0455162045524704</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5191,21 +5191,21 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1443</v>
+        <v>1219</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>215.0035259631712</v>
+        <v>219.2130601496071</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>0</v>
+        <v>10.85</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>6.806273921448437</v>
+        <v>29.84984847644951</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>15.50529927038307</v>
+        <v>32.41562580832303</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.0209071952831597</v>
+        <v>0.4333886196584854</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-1.688051536233574</v>
+        <v>-0.0493446006715273</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>209.4120223892369</v>
+        <v>215.0035259631712</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>45.09490377364582</v>
+        <v>6.806273921448437</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>17.12272799330464</v>
+        <v>15.50529927038307</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5505305263129875</v>
+        <v>0.0209071952831597</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.0559738053225184</v>
+        <v>-1.688051536233574</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1444</v>
+        <v>1447</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>208.8955571231655</v>
+        <v>209.4120223892369</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>7.14</v>
+        <v>7</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>39.77366605803847</v>
+        <v>45.09490377364582</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>17.54805305213702</v>
+        <v>17.12272799330464</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.5156243307289367</v>
+        <v>0.5505305263129875</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0597793834287579</v>
+        <v>-0.0559738053225184</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5350,21 +5350,21 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1256</v>
+        <v>1444</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>207.6001643176625</v>
+        <v>208.8955571231655</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>179.5</v>
+        <v>7.14</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>46.06483436680948</v>
+        <v>39.77366605803847</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>11.74064146978349</v>
+        <v>17.54805305213702</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.6310729198588259</v>
+        <v>0.5156243307289367</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.4268330475466766</v>
+        <v>-0.0597793834287579</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5403,21 +5403,21 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1521</v>
+        <v>1256</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>202.6294204868072</v>
+        <v>207.6001643176625</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>25</v>
+        <v>179.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>43.34300136902065</v>
+        <v>46.06483436680948</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>10.04667935292868</v>
+        <v>11.74064146978349</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.093655502116753</v>
+        <v>0.6310729198588259</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0233316506994599</v>
+        <v>-0.4268330475466766</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1419</v>
+        <v>1521</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>200.5500968743816</v>
+        <v>202.6294204868072</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>25</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>46.08542102801548</v>
+        <v>43.34300136902065</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>17.83002624687304</v>
+        <v>10.04667935292868</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.3990134031517092</v>
+        <v>1.093655502116753</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.3836923131189492</v>
+        <v>0.0233316506994599</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1527</v>
+        <v>1419</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>199.9126218872257</v>
+        <v>200.5500968743816</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>32.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>41.95740119275134</v>
+        <v>46.08542102801548</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>19.66140543579565</v>
+        <v>17.83002624687304</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.6440376355551887</v>
+        <v>0.3990134031517092</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.108051768222301</v>
+        <v>-0.3836923131189492</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1231</v>
+        <v>1527</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>196.2821189341836</v>
+        <v>199.9126218872257</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>81.2</v>
+        <v>32.7</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>35.93729296812789</v>
+        <v>41.95740119275134</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>25.57392764919722</v>
+        <v>19.66140543579565</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.376428847718512</v>
+        <v>0.6440376355551887</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.7832227697582455</v>
+        <v>-0.108051768222301</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1314</v>
+        <v>1231</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>194.6346211174784</v>
+        <v>196.2821189341836</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>7.7</v>
+        <v>81.2</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>41.71106878005602</v>
+        <v>35.93729296812789</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>16.38305620991552</v>
+        <v>25.57392764919722</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.6231181124837549</v>
+        <v>0.376428847718512</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0330245566965948</v>
+        <v>-0.7832227697582455</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1109</v>
+        <v>1314</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>192.6706210545122</v>
+        <v>194.6346211174784</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>13.55</v>
+        <v>7.7</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>29.25601552392004</v>
+        <v>41.71106878005602</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>38.37973577514566</v>
+        <v>16.38305620991552</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.442150838050235</v>
+        <v>0.6231181124837549</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0008679986780065</v>
+        <v>-0.0330245566965948</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1569</v>
+        <v>1109</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>184.1645390407753</v>
+        <v>192.6706210545122</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>41.3</v>
+        <v>13.55</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>43.46312156676496</v>
+        <v>29.25601552392004</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>20.95645242947473</v>
+        <v>38.37973577514566</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.6296966816016506</v>
+        <v>0.442150838050235</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.4400062094859684</v>
+        <v>-0.0008679986780065</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5774,21 +5774,21 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1423</v>
+        <v>1569</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>183.242632248815</v>
+        <v>184.1645390407753</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>36.1</v>
+        <v>41.3</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>43.90421075368439</v>
+        <v>43.46312156676496</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>13.50077323467092</v>
+        <v>20.95645242947473</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.1143038621650049</v>
+        <v>0.6296966816016506</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.1935214912083651</v>
+        <v>0.4400062094859684</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1452</v>
+        <v>1423</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>183.2248421284207</v>
+        <v>183.242632248815</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>11.3</v>
+        <v>36.1</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>48.06167399094921</v>
+        <v>43.90421075368439</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>21.94586058155053</v>
+        <v>13.50077323467092</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.1618942703128234</v>
+        <v>0.1143038621650049</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0317541729860839</v>
+        <v>0.1935214912083651</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1218</v>
+        <v>1452</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>176.6114355656757</v>
+        <v>183.2248421284207</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>15.7</v>
+        <v>11.3</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>39.46950951941917</v>
+        <v>48.06167399094921</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>39.11674475434982</v>
+        <v>21.94586058155053</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.3111398497880138</v>
+        <v>0.1618942703128234</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0533643280950334</v>
+        <v>-0.0317541729860839</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5933,21 +5933,21 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1471</v>
+        <v>1218</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>176.5951935163897</v>
+        <v>176.6114355656757</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>9.42</v>
+        <v>15.7</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>37.81483719631733</v>
+        <v>39.46950951941917</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>30.73729545857048</v>
+        <v>39.11674475434982</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.3158347293865693</v>
+        <v>0.3111398497880138</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0315377654999653</v>
+        <v>0.0533643280950334</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1441</v>
+        <v>1471</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>173.2737245063314</v>
+        <v>176.5951935163897</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>8.880000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>40.90161545762687</v>
+        <v>37.81483719631733</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>13.85579901548079</v>
+        <v>30.73729545857048</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.4783044866990302</v>
+        <v>0.3158347293865693</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0044174176995405</v>
+        <v>0.0315377654999653</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1460</v>
+        <v>1441</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>171.0035595547846</v>
+        <v>173.2737245063314</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>6.67</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>41.43312189839514</v>
+        <v>40.90161545762687</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>19.19232424904534</v>
+        <v>13.85579901548079</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.3967075146959484</v>
+        <v>0.4783044866990302</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0074243619199491</v>
+        <v>-0.0044174176995405</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1103</v>
+        <v>1460</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>165.1948712485943</v>
+        <v>171.0035595547846</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>13.2</v>
+        <v>6.67</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>46.84546749732182</v>
+        <v>41.43312189839514</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>9.884484033895101</v>
+        <v>19.19232424904534</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.3090885054909056</v>
+        <v>0.3967075146959484</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0018796395049161</v>
+        <v>-0.0074243619199491</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1464</v>
+        <v>1103</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>164.6999891184799</v>
+        <v>165.1948712485943</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>10.2</v>
+        <v>13.2</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>41.51707458301247</v>
+        <v>46.84546749732182</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>11.85171679497703</v>
+        <v>9.884484033895101</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.080565769019064</v>
+        <v>0.3090885054909056</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0135112335634628</v>
+        <v>-0.0018796395049161</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1340</v>
+        <v>1464</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>161.5924598294864</v>
+        <v>164.6999891184799</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>5.22</v>
+        <v>10.2</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>48.39797492634564</v>
+        <v>41.51707458301247</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>14.95063709943445</v>
+        <v>11.85171679497703</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.9971835188334102</v>
+        <v>1.080565769019064</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0197730460966117</v>
+        <v>-0.0135112335634628</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1324</v>
+        <v>1340</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>159.7262090460912</v>
+        <v>161.5924598294864</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>10</v>
+        <v>5.22</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>38.27356058266657</v>
+        <v>48.39797492634564</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>20.24900187956593</v>
+        <v>14.95063709943445</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.5860096968579928</v>
+        <v>0.9971835188334102</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0027606159461431</v>
+        <v>0.0197730460966117</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>1445</v>
+        <v>1324</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>159.4162161887573</v>
+        <v>159.7262090460912</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>35.65574245651197</v>
+        <v>38.27356058266657</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>14.85632724537385</v>
+        <v>20.24900187956593</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>2.343873232991048</v>
+        <v>0.5860096968579928</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0377351945073752</v>
+        <v>-0.0027606159461431</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1417</v>
+        <v>1445</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>155.5939198184679</v>
+        <v>159.4162161887573</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>42.25116433411226</v>
+        <v>35.65574245651197</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>17.29887063083568</v>
+        <v>14.85632724537385</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.5235191522409945</v>
+        <v>2.343873232991048</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0114023771926006</v>
+        <v>-0.0377351945073752</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1307</v>
+        <v>1417</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>154.6904734419033</v>
+        <v>155.5939198184679</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>31</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>40.93228664206995</v>
+        <v>42.25116433411226</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>19.61633505200849</v>
+        <v>17.29887063083568</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.190142112953289</v>
+        <v>0.5235191522409945</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0445653973627175</v>
+        <v>-0.0114023771926006</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1465</v>
+        <v>1307</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>153.0639454343883</v>
+        <v>154.6904734419033</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>12.35</v>
+        <v>31</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>43.05764447079241</v>
+        <v>40.93228664206995</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>16.96156964568107</v>
+        <v>19.61633505200849</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.445931723767654</v>
+        <v>1.190142112953289</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0446554167806016</v>
+        <v>0.0445653973627175</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1310</v>
+        <v>1465</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>149.3499320037301</v>
+        <v>153.0639454343883</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>8.01</v>
+        <v>12.35</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>40.15453483050887</v>
+        <v>43.05764447079241</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>24.72684396208632</v>
+        <v>16.96156964568107</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.4932798981224586</v>
+        <v>1.445931723767654</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0432906460119342</v>
+        <v>-0.0446554167806016</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1453</v>
+        <v>1310</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>148.0950960124609</v>
+        <v>149.3499320037301</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>11</v>
+        <v>8.01</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>41.41356195615577</v>
+        <v>40.15453483050887</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>11.68268299147238</v>
+        <v>24.72684396208632</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.242951253100346</v>
+        <v>0.4932798981224586</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0011431503523022</v>
+        <v>-0.0432906460119342</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1308</v>
+        <v>1453</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>147.90618277818</v>
+        <v>148.0950960124609</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>13.6</v>
+        <v>11</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>49.9857400753995</v>
+        <v>41.41356195615577</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>15.62572146107484</v>
+        <v>11.68268299147238</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.447303625892183</v>
+        <v>1.242951253100346</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.0483853032256053</v>
+        <v>0.0011431503523022</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>141.2804830643475</v>
+        <v>147.90618277818</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>11.6</v>
+        <v>13.6</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>43.67448989557877</v>
+        <v>49.9857400753995</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>20.86873829409741</v>
+        <v>15.62572146107484</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.40269231302901</v>
+        <v>0.447303625892183</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0422393066368323</v>
+        <v>0.0483853032256053</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1466</v>
+        <v>1305</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>138.2796558721365</v>
+        <v>141.2804830643475</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>16.75</v>
+        <v>11.6</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>52.89046359236711</v>
+        <v>43.67448989557877</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>14.82385098817253</v>
+        <v>20.86873829409741</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.3917078348145792</v>
+        <v>0.40269231302901</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0265282767256548</v>
+        <v>0.0422393066368323</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>1538</v>
+        <v>1466</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>134.7339095318641</v>
+        <v>138.2796558721365</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>0</v>
+        <v>16.75</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>41.29875941602906</v>
+        <v>52.89046359236711</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>11.36439215077821</v>
+        <v>14.82385098817253</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.1278466767984964</v>
+        <v>0.3917078348145792</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.6875866537400115</v>
+        <v>-0.0265282767256548</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1316</v>
+        <v>1538</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>132.0214571710662</v>
+        <v>134.7339095318641</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>10.05</v>
+        <v>0</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>46.41944271004674</v>
+        <v>41.29875941602906</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>18.46284560816941</v>
+        <v>11.36439215077821</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.140752245363488</v>
+        <v>0.1278466767984964</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0249144619060612</v>
+        <v>-0.6875866537400115</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1530</v>
+        <v>1316</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>127.2508037847454</v>
+        <v>132.0214571710662</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>28.8</v>
+        <v>10.05</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>50.88882086795783</v>
+        <v>46.41944271004674</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>14.91812611836302</v>
+        <v>18.46284560816941</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.320558380888634</v>
+        <v>1.140752245363488</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.0244108956238988</v>
+        <v>0.0249144619060612</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1473</v>
+        <v>1530</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>118.7403611290541</v>
+        <v>127.2508037847454</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>20.2</v>
+        <v>28.8</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>53.5152547540016</v>
+        <v>50.88882086795783</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>10.35634474493456</v>
+        <v>14.91812611836302</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.9398258951527576</v>
+        <v>1.320558380888634</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.0288916865594761</v>
+        <v>-0.0244108956238988</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>1201</v>
+        <v>1473</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>109.0287385332113</v>
+        <v>118.7403611290541</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>12.15</v>
+        <v>20.2</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>43.34153673638144</v>
+        <v>53.5152547540016</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>14.36761504298083</v>
+        <v>10.35634474493456</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.5595407274326305</v>
+        <v>0.9398258951527576</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.0241226169483534</v>
+        <v>0.0288916865594761</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1512</v>
+        <v>1201</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>108.7548303422406</v>
+        <v>109.0287385332113</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>6.56</v>
+        <v>12.15</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>38.54876614051038</v>
+        <v>43.34153673638144</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>7.958844501590164</v>
+        <v>14.36761504298083</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>1.196229006680402</v>
+        <v>0.5595407274326305</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.0103729097377649</v>
+        <v>-0.0241226169483534</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>1217</v>
+        <v>1512</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>瑞利</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>107.8777210717266</v>
+        <v>108.7548303422406</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>9.859999999999999</v>
+        <v>6.56</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>47.11592025403583</v>
+        <v>38.54876614051038</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>13.03278118465502</v>
+        <v>7.958844501590164</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.5143083179223082</v>
+        <v>1.196229006680402</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.0164405298221473</v>
+        <v>-0.0103729097377649</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>1457</v>
+        <v>1217</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>宜進</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>106.2066743546402</v>
+        <v>107.8777210717266</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>14.15</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>44.64186373601491</v>
+        <v>47.11592025403583</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>16.57173195374148</v>
+        <v>13.03278118465502</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.4739596766612968</v>
+        <v>0.5143083179223082</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.0178062943773338</v>
+        <v>-0.0164405298221473</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7205,21 +7205,21 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>1474</v>
+        <v>1457</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>宜進</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>88.85221832579848</v>
+        <v>106.2066743546402</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>10.1</v>
+        <v>14.15</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>44.02569472849904</v>
+        <v>44.64186373601491</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>17.94982260696251</v>
+        <v>16.57173195374148</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.4260429256444622</v>
+        <v>0.4739596766612968</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.0301472075812826</v>
+        <v>-0.0178062943773338</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7258,21 +7258,21 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>1541</v>
+        <v>1474</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>弘裕</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>85.1756202593547</v>
+        <v>88.85221832579848</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>21.5</v>
+        <v>10.1</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>47.94570869060764</v>
+        <v>44.02569472849904</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>15.92894658730088</v>
+        <v>17.94982260696251</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>1.141705109387013</v>
+        <v>0.4260429256444622</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.0131208462241497</v>
+        <v>-0.0301472075812826</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7311,21 +7311,21 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>1454</v>
+        <v>1541</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>錩泰</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>74.9533524148911</v>
+        <v>85.1756202593547</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>12.8</v>
+        <v>21.5</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,13 +7336,13 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>49.10493330530014</v>
+        <v>47.94570869060764</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>13.63036279250622</v>
+        <v>15.92894658730088</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.0483698332468304</v>
+        <v>1.141705109387013</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.0088354275509194</v>
+        <v>0.0131208462241497</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7364,21 +7364,21 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>1410</v>
+        <v>1454</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>73.29452844858224</v>
+        <v>74.9533524148911</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>25.55</v>
+        <v>12.8</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,13 +7389,13 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>47.14520280849365</v>
+        <v>49.10493330530014</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>15.5539930481942</v>
+        <v>13.63036279250622</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.5253533917529305</v>
+        <v>0.0483698332468304</v>
       </c>
       <c r="K131" s="2" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.0283806817744566</v>
+        <v>0.0088354275509194</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7417,52 +7417,105 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>南染</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>73.29452844858224</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>25.55</v>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>47.14520280849365</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>15.5539930481942</v>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>0.5253533917529305</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N132" s="2" t="n">
+        <v>-0.0283806817744566</v>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
         <v>1540</v>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>喬福</t>
         </is>
       </c>
-      <c r="C132" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D132" s="2" t="n">
+      <c r="C133" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D133" s="2" t="n">
         <v>70.65099977145086</v>
       </c>
-      <c r="E132" s="2" t="n">
+      <c r="E133" s="2" t="n">
         <v>19.65</v>
       </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H132" s="2" t="n">
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H133" s="2" t="n">
         <v>37.48269195667442</v>
       </c>
-      <c r="I132" s="2" t="n">
+      <c r="I133" s="2" t="n">
         <v>19.77361548198614</v>
       </c>
-      <c r="J132" s="2" t="n">
+      <c r="J133" s="2" t="n">
         <v>0.5080683570063032</v>
       </c>
-      <c r="K132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M132" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N132" s="2" t="n">
+      <c r="K133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N133" s="2" t="n">
         <v>-0.0561420639281413</v>
       </c>
-      <c r="O132" s="2" t="inlineStr">
+      <c r="O133" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>

--- a/output/full_scan/batch_seq1_2026-08-11.xlsx
+++ b/output/full_scan/batch_seq1_2026-08-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O133"/>
+  <dimension ref="A1:O132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1852,21 +1852,21 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1515</v>
+        <v>1526</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>439.8770648506869</v>
+        <v>428.4759109220414</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>31.2</v>
+        <v>19</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>46.72458537026104</v>
+        <v>62.75214711496405</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>28.31322714400099</v>
+        <v>47.07115644144011</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.8149748214244018</v>
+        <v>0.6138151680119505</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.4343200920012054</v>
+        <v>0.0552545326348695</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1526</v>
+        <v>1309</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>428.4759109220414</v>
+        <v>411.1471602673082</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>62.75214711496405</v>
+        <v>41.52723007550689</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>47.07115644144011</v>
+        <v>17.19347174560159</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.6138151680119505</v>
+        <v>0.2595805477207436</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.0552545326348695</v>
+        <v>0.0060577706939364</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1309</v>
+        <v>1432</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>411.1471602673082</v>
+        <v>405.078930911528</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>13</v>
+        <v>15.3</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>41.52723007550689</v>
+        <v>50.95505930945949</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>17.19347174560159</v>
+        <v>25.75021420284398</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.2595805477207436</v>
+        <v>0.7003565239209463</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0060577706939364</v>
+        <v>0.081368304773151</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1432</v>
+        <v>1513</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>405.078930911528</v>
+        <v>400.5229534332893</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>15.3</v>
+        <v>160.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>50.95505930945949</v>
+        <v>49.04047904672418</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>25.75021420284398</v>
+        <v>22.50604274131634</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.7003565239209463</v>
+        <v>0.5462464149368093</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.081368304773151</v>
+        <v>0.9065710135636152</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1513</v>
+        <v>1229</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>400.5229534332893</v>
+        <v>398.7253107875764</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>160.5</v>
+        <v>41.9</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>49.04047904672418</v>
+        <v>57.24037125149674</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>22.50604274131634</v>
+        <v>11.16007037440771</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.5462464149368093</v>
+        <v>1.245792503546678</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.9065710135636152</v>
+        <v>0.1007382603771434</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1229</v>
+        <v>1216</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>398.7253107875764</v>
+        <v>398.297000859084</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>41.9</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>57.24037125149674</v>
+        <v>50.1964409922735</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>11.16007037440771</v>
+        <v>20.99773696870421</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.245792503546678</v>
+        <v>0.5454149520786722</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.1007382603771434</v>
+        <v>-0.1884441727940486</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1216</v>
+        <v>1203</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>398.297000859084</v>
+        <v>393.2520897619105</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>75.90000000000001</v>
+        <v>45.95</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>50.1964409922735</v>
+        <v>46.64434885790448</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>20.99773696870421</v>
+        <v>17.41118151636101</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5454149520786722</v>
+        <v>0.349592415381889</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.1884441727940486</v>
+        <v>-0.3570210599754435</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1203</v>
+        <v>1402</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>393.2520897619105</v>
+        <v>386.539634412052</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>45.95</v>
+        <v>27.3</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>46.64434885790448</v>
+        <v>49.20603350020566</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>17.41118151636101</v>
+        <v>14.80699676704839</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.349592415381889</v>
+        <v>1.037191326958304</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.3570210599754435</v>
+        <v>0.0206040355552508</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1402</v>
+        <v>1301</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>386.539634412052</v>
+        <v>378.0401564785786</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>27.3</v>
+        <v>55.6</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>49.20603350020566</v>
+        <v>46.74057288099788</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>14.80699676704839</v>
+        <v>15.20039199896169</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.037191326958304</v>
+        <v>0.3120562285440211</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.0206040355552508</v>
+        <v>-0.7035811163955719</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1301</v>
+        <v>1236</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>378.0401564785786</v>
+        <v>375.1119844147829</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>55.6</v>
+        <v>25.2</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>46.74057288099788</v>
+        <v>59.5586556866246</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15.20039199896169</v>
+        <v>19.06234052027171</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.3120562285440211</v>
+        <v>1.280616226502821</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.7035811163955719</v>
+        <v>0.2274209289217866</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1236</v>
+        <v>1442</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>375.1119844147829</v>
+        <v>374.655718306141</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>25.2</v>
+        <v>29.85</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>59.5586556866246</v>
+        <v>57.23588554203469</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>19.06234052027171</v>
+        <v>24.24708991662144</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.280616226502821</v>
+        <v>0.2412429812893633</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.2274209289217866</v>
+        <v>-0.0395705337941666</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>374.655718306141</v>
+        <v>373.8135866675879</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>29.85</v>
+        <v>28.85</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>57.23588554203469</v>
+        <v>61.84972237186542</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>24.24708991662144</v>
+        <v>16.31728842823736</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.2412429812893633</v>
+        <v>0.3918968276735593</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.0395705337941666</v>
+        <v>0.1443541984183658</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1439</v>
+        <v>1220</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>373.8135866675879</v>
+        <v>373.776142573578</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>28.85</v>
+        <v>11.15</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>61.84972237186542</v>
+        <v>33.45802888711818</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>16.31728842823736</v>
+        <v>34.97124943750534</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.3918968276735593</v>
+        <v>0.2328142041653543</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.1443541984183658</v>
+        <v>0.0021448243131632</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1220</v>
+        <v>1524</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>373.776142573578</v>
+        <v>370.7749466919198</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>11.15</v>
+        <v>27.2</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>33.45802888711818</v>
+        <v>50.22102785127304</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>34.97124943750534</v>
+        <v>28.81970801030623</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.2328142041653543</v>
+        <v>0.535257575535256</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.0021448243131632</v>
+        <v>0.2434948686576256</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1524</v>
+        <v>1210</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>370.7749466919198</v>
+        <v>369.1782588013367</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>27.2</v>
+        <v>53.9</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>50.22102785127304</v>
+        <v>38.17190071174548</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>28.81970801030623</v>
+        <v>30.88333434699631</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.535257575535256</v>
+        <v>1.034942097131946</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.2434948686576256</v>
+        <v>-0.5138513427947438</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1210</v>
+        <v>1472</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>369.1782588013367</v>
+        <v>367.9269438148242</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>53.9</v>
+        <v>89</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>38.17190071174548</v>
+        <v>51.75909569405253</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>30.88333434699631</v>
+        <v>9.650250644180369</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.034942097131946</v>
+        <v>0.2428603462103321</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.5138513427947438</v>
+        <v>1.335599387906937</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1472</v>
+        <v>1514</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>367.9269438148242</v>
+        <v>365.3196194390216</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.75909569405253</v>
+        <v>43.1768601429351</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>9.650250644180369</v>
+        <v>26.10629698568654</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.2428603462103321</v>
+        <v>0.4937826619144091</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>1.335599387906937</v>
+        <v>0.7221265755818056</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1514</v>
+        <v>1342</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>365.3196194390216</v>
+        <v>361.527173571217</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>102</v>
+        <v>102.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>43.1768601429351</v>
+        <v>42.56748006451972</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>26.10629698568654</v>
+        <v>28.56495767453353</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.4937826619144091</v>
+        <v>0.4496404737020364</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.7221265755818056</v>
+        <v>-0.3807760402849149</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1342</v>
+        <v>1437</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>361.527173571217</v>
+        <v>360.5152994955215</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>102.5</v>
+        <v>30.4</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>42.56748006451972</v>
+        <v>48.54091658269144</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>28.56495767453353</v>
+        <v>19.33954860545237</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.4496404737020364</v>
+        <v>0.4609809680333634</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.3807760402849149</v>
+        <v>-0.1566334052246537</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1437</v>
+        <v>1568</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>360.5152994955215</v>
+        <v>349.958833619381</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>30.4</v>
+        <v>28.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>48.54091658269144</v>
+        <v>41.45675142900744</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>19.33954860545237</v>
+        <v>22.74065462889284</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.4609809680333634</v>
+        <v>0.4044884569132074</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.1566334052246537</v>
+        <v>0.4319178457368897</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1568</v>
+        <v>1326</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>349.958833619381</v>
+        <v>346.9668781509539</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>28.5</v>
+        <v>58.2</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>41.45675142900744</v>
+        <v>45.62903804524353</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>22.74065462889284</v>
+        <v>15.27378242141762</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4044884569132074</v>
+        <v>0.3405708815890401</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.4319178457368897</v>
+        <v>-0.8319722537334188</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1326</v>
+        <v>1477</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>346.9668781509539</v>
+        <v>335.9926556225922</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>58.2</v>
+        <v>221.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>45.62903804524353</v>
+        <v>51.31739932203453</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>15.27378242141762</v>
+        <v>11.5375287315453</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.3405708815890401</v>
+        <v>0.9441080317692208</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.8319722537334188</v>
+        <v>0.6385130704933423</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1477</v>
+        <v>1455</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>335.9926556225922</v>
+        <v>334.4210033697305</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>221.5</v>
+        <v>9.6</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>51.31739932203453</v>
+        <v>57.64588278442741</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>11.5375287315453</v>
+        <v>18.68329344736921</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.9441080317692208</v>
+        <v>1.910325167968465</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.6385130704933423</v>
+        <v>0.1046472799546037</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1455</v>
+        <v>1582</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>334.4210033697305</v>
+        <v>333.5994793960298</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>9.6</v>
+        <v>75.3</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>57.64588278442741</v>
+        <v>52.16051432114149</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>18.68329344736921</v>
+        <v>33.28133515949956</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.910325167968465</v>
+        <v>0.9692951731219532</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.1046472799546037</v>
+        <v>1.645062561429473</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1582</v>
+        <v>1321</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>333.5994793960298</v>
+        <v>332.9561939333805</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>75.3</v>
+        <v>31.95</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>52.16051432114149</v>
+        <v>52.38864746754686</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>33.28133515949956</v>
+        <v>14.93644998228591</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.9692951731219532</v>
+        <v>0.6188012648599847</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>1.645062561429473</v>
+        <v>-0.0609971870093484</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1321</v>
+        <v>1560</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>332.9561939333805</v>
+        <v>328.4934397084596</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>31.95</v>
+        <v>687</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>52.38864746754686</v>
+        <v>51.63913589547047</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>14.93644998228591</v>
+        <v>13.29765053865357</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.6188012648599847</v>
+        <v>0.4777662974194765</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.0609971870093484</v>
+        <v>4.338954788992442</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1560</v>
+        <v>1435</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>328.4934397084596</v>
+        <v>325.7701195109184</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>687</v>
+        <v>23.6</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>51.63913589547047</v>
+        <v>51.82647333983666</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>13.29765053865357</v>
+        <v>8.066518233274861</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.4777662974194765</v>
+        <v>1.236170837135644</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>4.338954788992442</v>
+        <v>-0.0872474229168677</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1435</v>
+        <v>1325</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>325.7701195109184</v>
+        <v>324.263616200573</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>23.6</v>
+        <v>26.3</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>51.82647333983666</v>
+        <v>50.54850454000123</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>8.066518233274861</v>
+        <v>24.90075748257971</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.236170837135644</v>
+        <v>0.3872299629085262</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.0872474229168677</v>
+        <v>0.0012671451922932</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1325</v>
+        <v>1416</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>324.263616200573</v>
+        <v>320.3588606533316</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>26.3</v>
+        <v>10.95</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>50.54850454000123</v>
+        <v>50.46517771063932</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>24.90075748257971</v>
+        <v>22.57730660233251</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.3872299629085262</v>
+        <v>0.6756232447876569</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0012671451922932</v>
+        <v>0.0204150409481747</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1416</v>
+        <v>1413</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>320.3588606533316</v>
+        <v>319.9092469134781</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>10.95</v>
+        <v>9.49</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>50.46517771063932</v>
+        <v>49.82702655094291</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>22.57730660233251</v>
+        <v>16.69493946805939</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.6756232447876569</v>
+        <v>0.0387677475666024</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0204150409481747</v>
+        <v>-0.0351350246016526</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1413</v>
+        <v>1522</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>319.9092469134781</v>
+        <v>314.659843995527</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>9.49</v>
+        <v>28.25</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>49.82702655094291</v>
+        <v>45.60192400140237</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>16.69493946805939</v>
+        <v>22.07775329046874</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.0387677475666024</v>
+        <v>0.779767028247413</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.0351350246016526</v>
+        <v>0.12716147982228</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1522</v>
+        <v>1436</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>314.659843995527</v>
+        <v>313.8827628490332</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>28.25</v>
+        <v>37.25</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>45.60192400140237</v>
+        <v>36.26396605298567</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>22.07775329046874</v>
+        <v>37.38851424097656</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.779767028247413</v>
+        <v>0.228140315722467</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.12716147982228</v>
+        <v>0.1030838199030017</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1436</v>
+        <v>1468</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>313.8827628490332</v>
+        <v>310.9208066965225</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>37.25</v>
+        <v>13.4</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>36.26396605298567</v>
+        <v>52.20630094666465</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>37.38851424097656</v>
+        <v>31.52311768412051</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.228140315722467</v>
+        <v>0.5578539685977438</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.1030838199030017</v>
+        <v>-0.068014350225212</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1468</v>
+        <v>1533</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>310.9208066965225</v>
+        <v>310.1160157782964</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>13.4</v>
+        <v>32.1</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>52.20630094666465</v>
+        <v>39.55794984681347</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>31.52311768412051</v>
+        <v>30.25908270005224</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.5578539685977438</v>
+        <v>1.301004634303973</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.068014350225212</v>
+        <v>0.1399299995070516</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1533</v>
+        <v>1519</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>310.1160157782964</v>
+        <v>307.637314419185</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>32.1</v>
+        <v>703</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>39.55794984681347</v>
+        <v>49.36152926987168</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>30.25908270005224</v>
+        <v>27.42060686359899</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.301004634303973</v>
+        <v>1.388798476689908</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.1399299995070516</v>
+        <v>4.003224569744347</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1519</v>
+        <v>1215</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>307.637314419185</v>
+        <v>305.6854120135607</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>703</v>
+        <v>109</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>49.36152926987168</v>
+        <v>48.76907478001936</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>27.42060686359899</v>
+        <v>43.24224320662321</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.388798476689908</v>
+        <v>0.8570895229183785</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>4.003224569744347</v>
+        <v>0.7469003322494432</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1215</v>
+        <v>1467</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>305.6854120135607</v>
+        <v>305.0546136737315</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>109</v>
+        <v>9.17</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>48.76907478001936</v>
+        <v>48.53640688787144</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>43.24224320662321</v>
+        <v>17.32432939492621</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.8570895229183785</v>
+        <v>0.6055603243375735</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.7469003322494432</v>
+        <v>-0.1112893337336087</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1467</v>
+        <v>1418</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>305.0546136737315</v>
+        <v>300.0311915161025</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>9.17</v>
+        <v>18</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>48.53640688787144</v>
+        <v>44.72896997235359</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>17.32432939492621</v>
+        <v>20.00581859068063</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.6055603243375735</v>
+        <v>0.1250649643009007</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.1112893337336087</v>
+        <v>-0.0467437114203713</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1418</v>
+        <v>1506</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>300.0311915161025</v>
+        <v>295.6373793354758</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>18</v>
+        <v>10.6</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>44.72896997235359</v>
+        <v>53.65486434981683</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>20.00581859068063</v>
+        <v>22.568653942497</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.1250649643009007</v>
+        <v>0.662196137200293</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.0467437114203713</v>
+        <v>-0.0147692095457922</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1506</v>
+        <v>1503</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>295.6373793354758</v>
+        <v>293.4261847870686</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>10.6</v>
+        <v>197</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>53.65486434981683</v>
+        <v>43.6172329224509</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>22.568653942497</v>
+        <v>27.79524027812574</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.662196137200293</v>
+        <v>0.9296184789241294</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0147692095457922</v>
+        <v>0.812910899986603</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1503</v>
+        <v>1463</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>293.4261847870686</v>
+        <v>291.2907683733289</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>197</v>
+        <v>17.85</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>43.6172329224509</v>
+        <v>52.73546460473577</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>27.79524027812574</v>
+        <v>14.36679042525562</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.9296184789241294</v>
+        <v>0.5434658532705821</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.812910899986603</v>
+        <v>-0.0034416952710157</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1463</v>
+        <v>1476</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>291.2907683733289</v>
+        <v>280.4916981673899</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>17.85</v>
+        <v>332</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>52.73546460473577</v>
+        <v>44.65722516107578</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>14.36679042525562</v>
+        <v>19.3404422990824</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.5434658532705821</v>
+        <v>0.8896667997248175</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.0034416952710157</v>
+        <v>-1.00678659863362</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1476</v>
+        <v>1536</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>280.4916981673899</v>
+        <v>275.6339257801737</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>332</v>
+        <v>51.2</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>44.65722516107578</v>
+        <v>53.22227897639052</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>19.3404422990824</v>
+        <v>13.69494818252926</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.8896667997248175</v>
+        <v>0.5003160922249125</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-1.00678659863362</v>
+        <v>0.3159899699966763</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1536</v>
+        <v>1102</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>275.6339257801737</v>
+        <v>272.4557755880668</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>51.2</v>
+        <v>32.45</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>53.22227897639052</v>
+        <v>38.52383346215739</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>13.69494818252926</v>
+        <v>28.43353066573429</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5003160922249125</v>
+        <v>0.5836679658648454</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.3159899699966763</v>
+        <v>0.0405050734409524</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1102</v>
+        <v>1108</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>272.4557755880668</v>
+        <v>271.9993124605894</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>32.45</v>
+        <v>11.85</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>38.52383346215739</v>
+        <v>29.19594336004857</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>28.43353066573429</v>
+        <v>56.14770979138584</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.5836679658648454</v>
+        <v>1.976228750469454</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0405050734409524</v>
+        <v>0.0409320313520392</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1108</v>
+        <v>1409</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>271.9993124605894</v>
+        <v>270.9907741070269</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>11.85</v>
+        <v>24.25</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>29.19594336004857</v>
+        <v>52.66905792945346</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>56.14770979138584</v>
+        <v>18.25778491805627</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.976228750469454</v>
+        <v>2.177057795327413</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.0409320313520392</v>
+        <v>0.2752931197043329</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1409</v>
+        <v>1304</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>270.9907741070269</v>
+        <v>270.5004804779987</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>24.25</v>
+        <v>11.95</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>52.66905792945346</v>
+        <v>44.62243479569965</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>18.25778491805627</v>
+        <v>15.99394048986938</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>2.177057795327413</v>
+        <v>0.4092229600487194</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.2752931197043329</v>
+        <v>0.0265786774749629</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1304</v>
+        <v>1475</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>270.5004804779987</v>
+        <v>266.432064011262</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>11.95</v>
+        <v>27.15</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>44.62243479569965</v>
+        <v>51.16923656774865</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>15.99394048986938</v>
+        <v>10.78818503948649</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4092229600487194</v>
+        <v>1.808096588343658</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0265786774749629</v>
+        <v>0.00694925957315</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
+          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1475</v>
+        <v>1438</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>266.432064011262</v>
+        <v>264.0955427232427</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>27.15</v>
+        <v>22.45</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>51.16923656774865</v>
+        <v>52.23340084143064</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>10.78818503948649</v>
+        <v>16.29996512183295</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.808096588343658</v>
+        <v>0.3929952472616391</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.00694925957315</v>
+        <v>0.009462815416149699</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1438</v>
+        <v>1233</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>264.0955427232427</v>
+        <v>259.9502512096455</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>22.45</v>
+        <v>28</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>52.23340084143064</v>
+        <v>36.81477639092548</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>16.29996512183295</v>
+        <v>32.07628624210136</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.3929952472616391</v>
+        <v>1.014648476212135</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.009462815416149699</v>
+        <v>-0.1111812470943652</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1233</v>
+        <v>1313</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>259.9502512096455</v>
+        <v>259.4469976615495</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>28</v>
+        <v>11.3</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>36.81477639092548</v>
+        <v>47.18557367471468</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>32.07628624210136</v>
+        <v>18.98486064721317</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.014648476212135</v>
+        <v>0.5511560768368882</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.1111812470943652</v>
+        <v>0.0364108069190954</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1313</v>
+        <v>1227</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>259.4469976615495</v>
+        <v>253.8586762490984</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>11.3</v>
+        <v>28.9</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>47.18557367471468</v>
+        <v>44.17793449682099</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>18.98486064721317</v>
+        <v>16.52284409359486</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5511560768368882</v>
+        <v>0.5803277779561153</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0364108069190954</v>
+        <v>-0.0743668604423379</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1227</v>
+        <v>1338</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>253.8586762490984</v>
+        <v>252.9277541118056</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>28.9</v>
+        <v>15.15</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>44.17793449682099</v>
+        <v>36.13085969525946</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>16.52284409359486</v>
+        <v>36.5596882507276</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5803277779561153</v>
+        <v>3.049368076886422</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0743668604423379</v>
+        <v>-0.0135561217104166</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1338</v>
+        <v>1528</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>252.9277541118056</v>
+        <v>246.4752653612645</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>15.15</v>
+        <v>19</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>36.13085969525946</v>
+        <v>42.04039258691191</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>36.5596882507276</v>
+        <v>41.87905566255956</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>3.049368076886422</v>
+        <v>0.6875115567800089</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0135561217104166</v>
+        <v>0.3047031127828075</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1528</v>
+        <v>1504</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>246.4752653612645</v>
+        <v>245.4422143653678</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>19</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>42.04039258691191</v>
+        <v>51.45156067236398</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>41.87905566255956</v>
+        <v>11.57477797473525</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6875115567800089</v>
+        <v>0.444833505570157</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.3047031127828075</v>
+        <v>0.4623565815650583</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1504</v>
+        <v>1446</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>245.4422143653678</v>
+        <v>243.1136378083713</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>14</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>51.45156067236398</v>
+        <v>38.42219195091725</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>11.57477797473525</v>
+        <v>39.28842303972318</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.444833505570157</v>
+        <v>0.4005502340837044</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.4623565815650583</v>
+        <v>0.1058207990009343</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1446</v>
+        <v>1529</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>243.1136378083713</v>
+        <v>242.1320414974783</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>14</v>
+        <v>16.9</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>38.42219195091725</v>
+        <v>28.46181352921619</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>39.28842303972318</v>
+        <v>36.92616172379231</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4005502340837044</v>
+        <v>0.6761317741182674</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.1058207990009343</v>
+        <v>0.0435452993768699</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1529</v>
+        <v>1456</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>242.1320414974783</v>
+        <v>231.2259258617373</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>16.9</v>
+        <v>13.8</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>28.46181352921619</v>
+        <v>46.16011168106276</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>36.92616172379231</v>
+        <v>13.32326001596232</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.6761317741182674</v>
+        <v>0.9248609937212076</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0435452993768699</v>
+        <v>0.0223855591722976</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1456</v>
+        <v>1104</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>231.2259258617373</v>
+        <v>230.1318115532384</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>13.8</v>
+        <v>26.65</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>46.16011168106276</v>
+        <v>44.87824851463436</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>13.32326001596232</v>
+        <v>15.47584064855316</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.9248609937212076</v>
+        <v>0.5877999785201938</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0223855591722976</v>
+        <v>0.0351395249502984</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1104</v>
+        <v>1532</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>230.1318115532384</v>
+        <v>229.7050742228243</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>26.65</v>
+        <v>21.85</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>44.87824851463436</v>
+        <v>42.03586421936555</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>15.47584064855316</v>
+        <v>27.00587128638867</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5877999785201938</v>
+        <v>0.4794046410191419</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0351395249502984</v>
+        <v>-0.089367138876109</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1532</v>
+        <v>1535</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>229.7050742228243</v>
+        <v>227.9082928094179</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>21.85</v>
+        <v>46.05</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>42.03586421936555</v>
+        <v>39.44157396367929</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>27.00587128638867</v>
+        <v>19.1260934601327</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.4794046410191419</v>
+        <v>0.5501484551371674</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.089367138876109</v>
+        <v>0.0954324712378362</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1535</v>
+        <v>1225</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>中宇</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>227.9082928094179</v>
+        <v>219.3071323708781</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>46.05</v>
+        <v>24.6</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>39.44157396367929</v>
+        <v>36.55030615302968</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>19.1260934601327</v>
+        <v>33.10128009326493</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5501484551371674</v>
+        <v>0.7221247272283944</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0954324712378362</v>
+        <v>-0.0455162045524704</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1225</v>
+        <v>1219</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>219.3071323708781</v>
+        <v>219.2130601496071</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>24.6</v>
+        <v>10.85</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>36.55030615302968</v>
+        <v>29.84984847644951</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>33.10128009326493</v>
+        <v>32.41562580832303</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.7221247272283944</v>
+        <v>0.4333886196584854</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0455162045524704</v>
+        <v>-0.0493446006715273</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5191,21 +5191,21 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1219</v>
+        <v>1443</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>219.2130601496071</v>
+        <v>215.0035259631712</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>10.85</v>
+        <v>0</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>29.84984847644951</v>
+        <v>6.806273921448437</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>32.41562580832303</v>
+        <v>15.50529927038307</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.4333886196584854</v>
+        <v>0.0209071952831597</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0493446006715273</v>
+        <v>-1.688051536233574</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>215.0035259631712</v>
+        <v>209.4120223892369</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>6.806273921448437</v>
+        <v>45.09490377364582</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>15.50529927038307</v>
+        <v>17.12272799330464</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.0209071952831597</v>
+        <v>0.5505305263129875</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-1.688051536233574</v>
+        <v>-0.0559738053225184</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>209.4120223892369</v>
+        <v>208.8955571231655</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>7</v>
+        <v>7.14</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>45.09490377364582</v>
+        <v>39.77366605803847</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>17.12272799330464</v>
+        <v>17.54805305213702</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.5505305263129875</v>
+        <v>0.5156243307289367</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0559738053225184</v>
+        <v>-0.0597793834287579</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5350,21 +5350,21 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1444</v>
+        <v>1256</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>208.8955571231655</v>
+        <v>207.6001643176625</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>7.14</v>
+        <v>179.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>39.77366605803847</v>
+        <v>46.06483436680948</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>17.54805305213702</v>
+        <v>11.74064146978349</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.5156243307289367</v>
+        <v>0.6310729198588259</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.0597793834287579</v>
+        <v>-0.4268330475466766</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5403,21 +5403,21 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1256</v>
+        <v>1521</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>207.6001643176625</v>
+        <v>202.6294204868072</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>179.5</v>
+        <v>25</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>46.06483436680948</v>
+        <v>43.34300136902065</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>11.74064146978349</v>
+        <v>10.04667935292868</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.6310729198588259</v>
+        <v>1.093655502116753</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.4268330475466766</v>
+        <v>0.0233316506994599</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1521</v>
+        <v>1419</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>202.6294204868072</v>
+        <v>200.5500968743816</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>25</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>43.34300136902065</v>
+        <v>46.08542102801548</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>10.04667935292868</v>
+        <v>17.83002624687304</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.093655502116753</v>
+        <v>0.3990134031517092</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0233316506994599</v>
+        <v>-0.3836923131189492</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1419</v>
+        <v>1527</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>200.5500968743816</v>
+        <v>199.9126218872257</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>32.7</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>46.08542102801548</v>
+        <v>41.95740119275134</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>17.83002624687304</v>
+        <v>19.66140543579565</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.3990134031517092</v>
+        <v>0.6440376355551887</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.3836923131189492</v>
+        <v>-0.108051768222301</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1527</v>
+        <v>1231</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>199.9126218872257</v>
+        <v>196.2821189341836</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>32.7</v>
+        <v>81.2</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>41.95740119275134</v>
+        <v>35.93729296812789</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>19.66140543579565</v>
+        <v>25.57392764919722</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.6440376355551887</v>
+        <v>0.376428847718512</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.108051768222301</v>
+        <v>-0.7832227697582455</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1231</v>
+        <v>1314</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>196.2821189341836</v>
+        <v>194.6346211174784</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>81.2</v>
+        <v>7.7</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>35.93729296812789</v>
+        <v>41.71106878005602</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>25.57392764919722</v>
+        <v>16.38305620991552</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.376428847718512</v>
+        <v>0.6231181124837549</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.7832227697582455</v>
+        <v>-0.0330245566965948</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1314</v>
+        <v>1109</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>194.6346211174784</v>
+        <v>192.6706210545122</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>7.7</v>
+        <v>13.55</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>41.71106878005602</v>
+        <v>29.25601552392004</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>16.38305620991552</v>
+        <v>38.37973577514566</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.6231181124837549</v>
+        <v>0.442150838050235</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0330245566965948</v>
+        <v>-0.0008679986780065</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1109</v>
+        <v>1569</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>192.6706210545122</v>
+        <v>184.1645390407753</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>13.55</v>
+        <v>41.3</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>29.25601552392004</v>
+        <v>43.46312156676496</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>38.37973577514566</v>
+        <v>20.95645242947473</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.442150838050235</v>
+        <v>0.6296966816016506</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.0008679986780065</v>
+        <v>0.4400062094859684</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5774,21 +5774,21 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1569</v>
+        <v>1423</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>184.1645390407753</v>
+        <v>183.242632248815</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>41.3</v>
+        <v>36.1</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>43.46312156676496</v>
+        <v>43.90421075368439</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>20.95645242947473</v>
+        <v>13.50077323467092</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.6296966816016506</v>
+        <v>0.1143038621650049</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.4400062094859684</v>
+        <v>0.1935214912083651</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1423</v>
+        <v>1452</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>183.242632248815</v>
+        <v>183.2248421284207</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>36.1</v>
+        <v>11.3</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>43.90421075368439</v>
+        <v>48.06167399094921</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>13.50077323467092</v>
+        <v>21.94586058155053</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.1143038621650049</v>
+        <v>0.1618942703128234</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.1935214912083651</v>
+        <v>-0.0317541729860839</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1452</v>
+        <v>1218</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>183.2248421284207</v>
+        <v>176.6114355656757</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>11.3</v>
+        <v>15.7</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>48.06167399094921</v>
+        <v>39.46950951941917</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>21.94586058155053</v>
+        <v>39.11674475434982</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.1618942703128234</v>
+        <v>0.3111398497880138</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0317541729860839</v>
+        <v>0.0533643280950334</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5933,21 +5933,21 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1218</v>
+        <v>1471</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>176.6114355656757</v>
+        <v>176.5951935163897</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>15.7</v>
+        <v>9.42</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>39.46950951941917</v>
+        <v>37.81483719631733</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>39.11674475434982</v>
+        <v>30.73729545857048</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.3111398497880138</v>
+        <v>0.3158347293865693</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0533643280950334</v>
+        <v>0.0315377654999653</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1471</v>
+        <v>1441</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>176.5951935163897</v>
+        <v>173.2737245063314</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>9.42</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>37.81483719631733</v>
+        <v>40.90161545762687</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>30.73729545857048</v>
+        <v>13.85579901548079</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.3158347293865693</v>
+        <v>0.4783044866990302</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.0315377654999653</v>
+        <v>-0.0044174176995405</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1441</v>
+        <v>1460</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>173.2737245063314</v>
+        <v>171.0035595547846</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>8.880000000000001</v>
+        <v>6.67</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>40.90161545762687</v>
+        <v>41.43312189839514</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>13.85579901548079</v>
+        <v>19.19232424904534</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.4783044866990302</v>
+        <v>0.3967075146959484</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0044174176995405</v>
+        <v>-0.0074243619199491</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1460</v>
+        <v>1103</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>171.0035595547846</v>
+        <v>165.1948712485943</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>6.67</v>
+        <v>13.2</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>41.43312189839514</v>
+        <v>46.84546749732182</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>19.19232424904534</v>
+        <v>9.884484033895101</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.3967075146959484</v>
+        <v>0.3090885054909056</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0074243619199491</v>
+        <v>-0.0018796395049161</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1103</v>
+        <v>1464</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>165.1948712485943</v>
+        <v>164.6999891184799</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>13.2</v>
+        <v>10.2</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>46.84546749732182</v>
+        <v>41.51707458301247</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>9.884484033895101</v>
+        <v>11.85171679497703</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3090885054909056</v>
+        <v>1.080565769019064</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0018796395049161</v>
+        <v>-0.0135112335634628</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1464</v>
+        <v>1340</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>164.6999891184799</v>
+        <v>161.5924598294864</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>10.2</v>
+        <v>5.22</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>41.51707458301247</v>
+        <v>48.39797492634564</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>11.85171679497703</v>
+        <v>14.95063709943445</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.080565769019064</v>
+        <v>0.9971835188334102</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0135112335634628</v>
+        <v>0.0197730460966117</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1340</v>
+        <v>1324</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>161.5924598294864</v>
+        <v>159.7262090460912</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>5.22</v>
+        <v>10</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>48.39797492634564</v>
+        <v>38.27356058266657</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>14.95063709943445</v>
+        <v>20.24900187956593</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.9971835188334102</v>
+        <v>0.5860096968579928</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0197730460966117</v>
+        <v>-0.0027606159461431</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>1324</v>
+        <v>1445</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>159.7262090460912</v>
+        <v>159.4162161887573</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>38.27356058266657</v>
+        <v>35.65574245651197</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>20.24900187956593</v>
+        <v>14.85632724537385</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.5860096968579928</v>
+        <v>2.343873232991048</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0027606159461431</v>
+        <v>-0.0377351945073752</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1445</v>
+        <v>1417</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>159.4162161887573</v>
+        <v>155.5939198184679</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>10.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>35.65574245651197</v>
+        <v>42.25116433411226</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>14.85632724537385</v>
+        <v>17.29887063083568</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>2.343873232991048</v>
+        <v>0.5235191522409945</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0377351945073752</v>
+        <v>-0.0114023771926006</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1417</v>
+        <v>1307</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>155.5939198184679</v>
+        <v>154.6904734419033</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>31</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>42.25116433411226</v>
+        <v>40.93228664206995</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>17.29887063083568</v>
+        <v>19.61633505200849</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5235191522409945</v>
+        <v>1.190142112953289</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0114023771926006</v>
+        <v>0.0445653973627175</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1307</v>
+        <v>1465</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>154.6904734419033</v>
+        <v>153.0639454343883</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>31</v>
+        <v>12.35</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>40.93228664206995</v>
+        <v>43.05764447079241</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>19.61633505200849</v>
+        <v>16.96156964568107</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.190142112953289</v>
+        <v>1.445931723767654</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0445653973627175</v>
+        <v>-0.0446554167806016</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1465</v>
+        <v>1310</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>153.0639454343883</v>
+        <v>149.3499320037301</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>12.35</v>
+        <v>8.01</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>43.05764447079241</v>
+        <v>40.15453483050887</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>16.96156964568107</v>
+        <v>24.72684396208632</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.445931723767654</v>
+        <v>0.4932798981224586</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0446554167806016</v>
+        <v>-0.0432906460119342</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1310</v>
+        <v>1453</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>149.3499320037301</v>
+        <v>148.0950960124609</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>8.01</v>
+        <v>11</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>40.15453483050887</v>
+        <v>41.41356195615577</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>24.72684396208632</v>
+        <v>11.68268299147238</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.4932798981224586</v>
+        <v>1.242951253100346</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0432906460119342</v>
+        <v>0.0011431503523022</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1453</v>
+        <v>1308</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>148.0950960124609</v>
+        <v>147.90618277818</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>11</v>
+        <v>13.6</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>41.41356195615577</v>
+        <v>49.9857400753995</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>11.68268299147238</v>
+        <v>15.62572146107484</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.242951253100346</v>
+        <v>0.447303625892183</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.0011431503523022</v>
+        <v>0.0483853032256053</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1308</v>
+        <v>1305</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>147.90618277818</v>
+        <v>141.2804830643475</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>13.6</v>
+        <v>11.6</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>49.9857400753995</v>
+        <v>43.67448989557877</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>15.62572146107484</v>
+        <v>20.86873829409741</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.447303625892183</v>
+        <v>0.40269231302901</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0483853032256053</v>
+        <v>0.0422393066368323</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1305</v>
+        <v>1466</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>141.2804830643475</v>
+        <v>138.2796558721365</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>11.6</v>
+        <v>16.75</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>43.67448989557877</v>
+        <v>52.89046359236711</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>20.86873829409741</v>
+        <v>14.82385098817253</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.40269231302901</v>
+        <v>0.3917078348145792</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.0422393066368323</v>
+        <v>-0.0265282767256548</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>1466</v>
+        <v>1538</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>138.2796558721365</v>
+        <v>134.7339095318641</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>16.75</v>
+        <v>0</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>52.89046359236711</v>
+        <v>41.29875941602906</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>14.82385098817253</v>
+        <v>11.36439215077821</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.3917078348145792</v>
+        <v>0.1278466767984964</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.0265282767256548</v>
+        <v>-0.6875866537400115</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, above_ichimoku_cloud</t>
+          <t>market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1538</v>
+        <v>1316</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>134.7339095318641</v>
+        <v>132.0214571710662</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>0</v>
+        <v>10.05</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>41.29875941602906</v>
+        <v>46.41944271004674</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>11.36439215077821</v>
+        <v>18.46284560816941</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.1278466767984964</v>
+        <v>1.140752245363488</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.6875866537400115</v>
+        <v>0.0249144619060612</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1316</v>
+        <v>1530</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>132.0214571710662</v>
+        <v>127.2508037847454</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>10.05</v>
+        <v>28.8</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>46.41944271004674</v>
+        <v>50.88882086795783</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>18.46284560816941</v>
+        <v>14.91812611836302</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.140752245363488</v>
+        <v>1.320558380888634</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.0249144619060612</v>
+        <v>-0.0244108956238988</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1530</v>
+        <v>1473</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>127.2508037847454</v>
+        <v>118.7403611290541</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>28.8</v>
+        <v>20.2</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>50.88882086795783</v>
+        <v>53.5152547540016</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>14.91812611836302</v>
+        <v>10.35634474493456</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1.320558380888634</v>
+        <v>0.9398258951527576</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.0244108956238988</v>
+        <v>0.0288916865594761</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>1473</v>
+        <v>1201</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>118.7403611290541</v>
+        <v>109.0287385332113</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>20.2</v>
+        <v>12.15</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>53.5152547540016</v>
+        <v>43.34153673638144</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>10.35634474493456</v>
+        <v>14.36761504298083</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.9398258951527576</v>
+        <v>0.5595407274326305</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0288916865594761</v>
+        <v>-0.0241226169483534</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1201</v>
+        <v>1512</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>瑞利</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>109.0287385332113</v>
+        <v>108.7548303422406</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>12.15</v>
+        <v>6.56</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>43.34153673638144</v>
+        <v>38.54876614051038</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>14.36761504298083</v>
+        <v>7.958844501590164</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.5595407274326305</v>
+        <v>1.196229006680402</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.0241226169483534</v>
+        <v>-0.0103729097377649</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>1512</v>
+        <v>1217</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>108.7548303422406</v>
+        <v>107.8777210717266</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>6.56</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>38.54876614051038</v>
+        <v>47.11592025403583</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>7.958844501590164</v>
+        <v>13.03278118465502</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>1.196229006680402</v>
+        <v>0.5143083179223082</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.0103729097377649</v>
+        <v>-0.0164405298221473</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>1217</v>
+        <v>1457</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>宜進</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>107.8777210717266</v>
+        <v>106.2066743546402</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>9.859999999999999</v>
+        <v>14.15</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>47.11592025403583</v>
+        <v>44.64186373601491</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>13.03278118465502</v>
+        <v>16.57173195374148</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.5143083179223082</v>
+        <v>0.4739596766612968</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.0164405298221473</v>
+        <v>-0.0178062943773338</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7205,21 +7205,21 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>1457</v>
+        <v>1474</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>宜進</t>
+          <t>弘裕</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>106.2066743546402</v>
+        <v>88.85221832579848</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>14.15</v>
+        <v>10.1</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>44.64186373601491</v>
+        <v>44.02569472849904</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>16.57173195374148</v>
+        <v>17.94982260696251</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.4739596766612968</v>
+        <v>0.4260429256444622</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.0178062943773338</v>
+        <v>-0.0301472075812826</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7258,21 +7258,21 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>1474</v>
+        <v>1541</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>錩泰</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>88.85221832579848</v>
+        <v>85.1756202593547</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>10.1</v>
+        <v>21.5</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>44.02569472849904</v>
+        <v>47.94570869060764</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>17.94982260696251</v>
+        <v>15.92894658730088</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.4260429256444622</v>
+        <v>1.141705109387013</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.0301472075812826</v>
+        <v>0.0131208462241497</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7311,21 +7311,21 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>1541</v>
+        <v>1454</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>85.1756202593547</v>
+        <v>74.9533524148911</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>21.5</v>
+        <v>12.8</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,13 +7336,13 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>47.94570869060764</v>
+        <v>49.10493330530014</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>15.92894658730088</v>
+        <v>13.63036279250622</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>1.141705109387013</v>
+        <v>0.0483698332468304</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.0131208462241497</v>
+        <v>0.0088354275509194</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7364,21 +7364,21 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>1454</v>
+        <v>1410</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>74.9533524148911</v>
+        <v>73.29452844858224</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>12.8</v>
+        <v>25.55</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,13 +7389,13 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>49.10493330530014</v>
+        <v>47.14520280849365</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>13.63036279250622</v>
+        <v>15.5539930481942</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.0483698332468304</v>
+        <v>0.5253533917529305</v>
       </c>
       <c r="K131" s="2" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>0.0088354275509194</v>
+        <v>-0.0283806817744566</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>1410</v>
+        <v>1540</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>喬福</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>73.29452844858224</v>
+        <v>70.65099977145086</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>25.55</v>
+        <v>19.65</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,13 +7442,13 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>47.14520280849365</v>
+        <v>37.48269195667442</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>15.5539930481942</v>
+        <v>19.77361548198614</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.5253533917529305</v>
+        <v>0.5080683570063032</v>
       </c>
       <c r="K132" s="2" t="n">
         <v>0</v>
@@ -7460,62 +7460,9 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-0.0283806817744566</v>
+        <v>-0.0561420639281413</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="n">
-        <v>1540</v>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>喬福</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D133" s="2" t="n">
-        <v>70.65099977145086</v>
-      </c>
-      <c r="E133" s="2" t="n">
-        <v>19.65</v>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H133" s="2" t="n">
-        <v>37.48269195667442</v>
-      </c>
-      <c r="I133" s="2" t="n">
-        <v>19.77361548198614</v>
-      </c>
-      <c r="J133" s="2" t="n">
-        <v>0.5080683570063032</v>
-      </c>
-      <c r="K133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M133" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N133" s="2" t="n">
-        <v>-0.0561420639281413</v>
-      </c>
-      <c r="O133" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
